--- a/Div_Roads Project.xlsx
+++ b/Div_Roads Project.xlsx
@@ -8,25 +8,35 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/b94b8e39c9d805aa/Documents/GitHub/Diverging-Roads/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="205" documentId="11_F25DC773A252ABDACC10484719DA7CD85BDE58F3" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{A32D937D-15D1-4EFB-BDB3-DE7598CEBA8A}"/>
+  <xr:revisionPtr revIDLastSave="223" documentId="11_F25DC773A252ABDACC10484719DA7CD85BDE58F3" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{2D617D15-C3FE-478A-BAF8-E3BFBE78907A}"/>
   <bookViews>
-    <workbookView xWindow="300" yWindow="240" windowWidth="18540" windowHeight="14505" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="18540" windowHeight="14505" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="162913"/>
-  <fileRecoveryPr repairLoad="1"/>
+  <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
+    </ext>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
     </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="92" uniqueCount="52">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="106" uniqueCount="52">
   <si>
     <t>Title</t>
   </si>
@@ -713,6 +723,9 @@
       <c r="J4" s="3" t="s">
         <v>33</v>
       </c>
+      <c r="L4" s="3" t="s">
+        <v>33</v>
+      </c>
     </row>
     <row r="5" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A5" s="3">
@@ -721,6 +734,9 @@
       <c r="B5" s="2" t="s">
         <v>7</v>
       </c>
+      <c r="C5" s="2">
+        <v>2737</v>
+      </c>
       <c r="D5" s="2">
         <v>2022</v>
       </c>
@@ -734,6 +750,9 @@
         <v>33</v>
       </c>
       <c r="J5" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="L5" s="3" t="s">
         <v>33</v>
       </c>
     </row>
@@ -744,10 +763,25 @@
       <c r="B6" s="2" t="s">
         <v>8</v>
       </c>
+      <c r="C6" s="2">
+        <v>4436</v>
+      </c>
       <c r="D6" s="2">
         <v>2022</v>
       </c>
       <c r="E6" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="F6" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="G6" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="J6" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="L6" s="3" t="s">
         <v>33</v>
       </c>
     </row>
@@ -758,10 +792,25 @@
       <c r="B7" s="2" t="s">
         <v>9</v>
       </c>
+      <c r="C7" s="2">
+        <v>500</v>
+      </c>
       <c r="D7" s="2">
         <v>2022</v>
       </c>
       <c r="E7" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="F7" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="G7" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="J7" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="L7" s="3" t="s">
         <v>33</v>
       </c>
     </row>
@@ -772,10 +821,25 @@
       <c r="B8" s="2" t="s">
         <v>13</v>
       </c>
+      <c r="C8" s="2">
+        <v>488</v>
+      </c>
       <c r="D8" s="2">
         <v>2022</v>
       </c>
       <c r="E8" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="F8" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="G8" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="J8" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="L8" s="3" t="s">
         <v>33</v>
       </c>
     </row>

--- a/Div_Roads Project.xlsx
+++ b/Div_Roads Project.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/b94b8e39c9d805aa/Documents/GitHub/Diverging-Roads/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="223" documentId="11_F25DC773A252ABDACC10484719DA7CD85BDE58F3" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{2D617D15-C3FE-478A-BAF8-E3BFBE78907A}"/>
+  <xr:revisionPtr revIDLastSave="256" documentId="11_F25DC773A252ABDACC10484719DA7CD85BDE58F3" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{EF4ADE64-D8E6-442A-9E93-175C62B43217}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="18540" windowHeight="14505" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -16,6 +16,7 @@
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
   <calcPr calcId="191029"/>
+  <fileRecoveryPr repairLoad="1"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -36,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="106" uniqueCount="52">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="124" uniqueCount="54">
   <si>
     <t>Title</t>
   </si>
@@ -192,6 +193,12 @@
   </si>
   <si>
     <t>Forced to fit, but need a generic external stylesheet solution.  ADD CAPTIONS TO WORD DOC IMAGES</t>
+  </si>
+  <si>
+    <t>Total:</t>
+  </si>
+  <si>
+    <t>Average</t>
   </si>
 </sst>
 </file>
@@ -250,7 +257,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="10">
+  <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
@@ -278,6 +285,9 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="1" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -850,10 +860,25 @@
       <c r="B9" s="2" t="s">
         <v>10</v>
       </c>
+      <c r="C9" s="2">
+        <v>1235</v>
+      </c>
       <c r="D9" s="2">
         <v>2023</v>
       </c>
       <c r="E9" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="F9" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="G9" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="J9" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="L9" s="3" t="s">
         <v>33</v>
       </c>
     </row>
@@ -864,10 +889,25 @@
       <c r="B10" s="2" t="s">
         <v>11</v>
       </c>
+      <c r="C10" s="2">
+        <v>1356</v>
+      </c>
       <c r="D10" s="2">
         <v>2023</v>
       </c>
       <c r="E10" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="F10" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="G10" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="J10" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="L10" s="3" t="s">
         <v>33</v>
       </c>
     </row>
@@ -878,10 +918,25 @@
       <c r="B11" s="2" t="s">
         <v>12</v>
       </c>
+      <c r="C11" s="2">
+        <v>2143</v>
+      </c>
       <c r="D11" s="2">
         <v>2023</v>
       </c>
       <c r="E11" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="F11" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="G11" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="J11" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="L11" s="3" t="s">
         <v>33</v>
       </c>
     </row>
@@ -898,6 +953,18 @@
       <c r="E12" s="4" t="s">
         <v>33</v>
       </c>
+      <c r="F12" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="G12" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="J12" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="L12" s="3" t="s">
+        <v>33</v>
+      </c>
     </row>
     <row r="13" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A13" s="3">
@@ -1147,52 +1214,70 @@
         <v>30</v>
       </c>
     </row>
-    <row r="35" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="B32" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="C32" s="2">
+        <f>SUM(C2:C31)</f>
+        <v>21188</v>
+      </c>
+    </row>
+    <row r="33" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="B33" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="C33" s="10">
+        <f>AVERAGE(C2:C31)</f>
+        <v>2118.8000000000002</v>
+      </c>
+    </row>
+    <row r="35" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A35" s="8" t="s">
         <v>48</v>
       </c>
     </row>
-    <row r="36" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A36" s="9" t="s">
         <v>49</v>
       </c>
     </row>
-    <row r="37" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A37" s="9" t="s">
         <v>50</v>
       </c>
     </row>
-    <row r="38" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A38" s="9"/>
     </row>
-    <row r="39" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A39" s="9"/>
     </row>
-    <row r="40" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A40" s="9"/>
     </row>
-    <row r="41" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A41" s="9"/>
     </row>
-    <row r="42" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A42" s="9"/>
     </row>
-    <row r="43" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A43" s="9"/>
     </row>
-    <row r="44" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A44" s="9"/>
     </row>
-    <row r="45" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A45" s="9"/>
     </row>
-    <row r="46" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A46" s="9"/>
     </row>
-    <row r="47" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A47" s="9"/>
     </row>
-    <row r="48" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A48" s="9"/>
     </row>
     <row r="49" spans="1:1" x14ac:dyDescent="0.25">

--- a/Div_Roads Project.xlsx
+++ b/Div_Roads Project.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/b94b8e39c9d805aa/Documents/GitHub/Diverging-Roads/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="256" documentId="11_F25DC773A252ABDACC10484719DA7CD85BDE58F3" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{EF4ADE64-D8E6-442A-9E93-175C62B43217}"/>
+  <xr:revisionPtr revIDLastSave="258" documentId="11_F25DC773A252ABDACC10484719DA7CD85BDE58F3" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{6FE6C09B-255E-41C4-AD32-F91F90CFC997}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="18540" windowHeight="14505" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView minimized="1" xWindow="0" yWindow="0" windowWidth="18540" windowHeight="14505" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -947,6 +947,9 @@
       <c r="B12" s="2" t="s">
         <v>14</v>
       </c>
+      <c r="C12" s="2">
+        <v>6216</v>
+      </c>
       <c r="D12" s="2">
         <v>2023</v>
       </c>
@@ -973,6 +976,9 @@
       <c r="B13" s="2" t="s">
         <v>15</v>
       </c>
+      <c r="C13" s="2">
+        <v>934</v>
+      </c>
       <c r="D13" s="2">
         <v>2023</v>
       </c>
@@ -1220,7 +1226,7 @@
       </c>
       <c r="C32" s="2">
         <f>SUM(C2:C31)</f>
-        <v>21188</v>
+        <v>28338</v>
       </c>
     </row>
     <row r="33" spans="1:3" x14ac:dyDescent="0.25">
@@ -1229,7 +1235,7 @@
       </c>
       <c r="C33" s="10">
         <f>AVERAGE(C2:C31)</f>
-        <v>2118.8000000000002</v>
+        <v>2361.5</v>
       </c>
     </row>
     <row r="35" spans="1:3" x14ac:dyDescent="0.25">

--- a/Div_Roads Project.xlsx
+++ b/Div_Roads Project.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/b94b8e39c9d805aa/Documents/GitHub/Diverging-Roads/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="258" documentId="11_F25DC773A252ABDACC10484719DA7CD85BDE58F3" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{6FE6C09B-255E-41C4-AD32-F91F90CFC997}"/>
+  <xr:revisionPtr revIDLastSave="263" documentId="11_F25DC773A252ABDACC10484719DA7CD85BDE58F3" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{B2A05A8A-3312-44AD-9F5E-0155754E173B}"/>
   <bookViews>
-    <workbookView minimized="1" xWindow="0" yWindow="0" windowWidth="18540" windowHeight="14505" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="825" yWindow="0" windowWidth="18540" windowHeight="14505" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="124" uniqueCount="54">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="128" uniqueCount="54">
   <si>
     <t>Title</t>
   </si>
@@ -985,6 +985,18 @@
       <c r="E13" s="4" t="s">
         <v>33</v>
       </c>
+      <c r="F13" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="G13" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="J13" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="L13" s="3" t="s">
+        <v>33</v>
+      </c>
     </row>
     <row r="14" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A14" s="3">
@@ -993,6 +1005,9 @@
       <c r="B14" s="2" t="s">
         <v>16</v>
       </c>
+      <c r="C14" s="2">
+        <v>12746</v>
+      </c>
       <c r="D14" s="2">
         <v>2023</v>
       </c>
@@ -1226,7 +1241,7 @@
       </c>
       <c r="C32" s="2">
         <f>SUM(C2:C31)</f>
-        <v>28338</v>
+        <v>41084</v>
       </c>
     </row>
     <row r="33" spans="1:3" x14ac:dyDescent="0.25">
@@ -1235,7 +1250,7 @@
       </c>
       <c r="C33" s="10">
         <f>AVERAGE(C2:C31)</f>
-        <v>2361.5</v>
+        <v>3160.3076923076924</v>
       </c>
     </row>
     <row r="35" spans="1:3" x14ac:dyDescent="0.25">

--- a/Div_Roads Project.xlsx
+++ b/Div_Roads Project.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/b94b8e39c9d805aa/Documents/GitHub/Diverging-Roads/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="263" documentId="11_F25DC773A252ABDACC10484719DA7CD85BDE58F3" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{B2A05A8A-3312-44AD-9F5E-0155754E173B}"/>
+  <xr:revisionPtr revIDLastSave="265" documentId="11_F25DC773A252ABDACC10484719DA7CD85BDE58F3" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00894A0A-5388-46B9-9EF8-5507959EB6DE}"/>
   <bookViews>
     <workbookView xWindow="825" yWindow="0" windowWidth="18540" windowHeight="14505" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="128" uniqueCount="54">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="130" uniqueCount="55">
   <si>
     <t>Title</t>
   </si>
@@ -199,6 +199,9 @@
   </si>
   <si>
     <t>Average</t>
+  </si>
+  <si>
+    <t>Fig 27b Angel mosaic not working in "Github" version</t>
   </si>
 </sst>
 </file>
@@ -940,7 +943,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="12" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:14" ht="45" x14ac:dyDescent="0.25">
       <c r="A12" s="3">
         <v>11</v>
       </c>
@@ -961,6 +964,9 @@
       </c>
       <c r="G12" s="3" t="s">
         <v>33</v>
+      </c>
+      <c r="H12" s="1" t="s">
+        <v>54</v>
       </c>
       <c r="J12" s="3" t="s">
         <v>33</v>
@@ -1012,6 +1018,9 @@
         <v>2023</v>
       </c>
       <c r="E14" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="F14" s="3" t="s">
         <v>33</v>
       </c>
     </row>

--- a/Div_Roads Project.xlsx
+++ b/Div_Roads Project.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/b94b8e39c9d805aa/Documents/GitHub/Diverging-Roads/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="265" documentId="11_F25DC773A252ABDACC10484719DA7CD85BDE58F3" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00894A0A-5388-46B9-9EF8-5507959EB6DE}"/>
+  <xr:revisionPtr revIDLastSave="268" documentId="11_F25DC773A252ABDACC10484719DA7CD85BDE58F3" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{32023ABA-61CD-4CE5-90AA-A550A20869B3}"/>
   <bookViews>
     <workbookView xWindow="825" yWindow="0" windowWidth="18540" windowHeight="14505" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="130" uniqueCount="55">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="133" uniqueCount="55">
   <si>
     <t>Title</t>
   </si>
@@ -1023,6 +1023,15 @@
       <c r="F14" s="3" t="s">
         <v>33</v>
       </c>
+      <c r="G14" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="J14" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="L14" s="3" t="s">
+        <v>33</v>
+      </c>
     </row>
     <row r="15" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A15" s="3">

--- a/Div_Roads Project.xlsx
+++ b/Div_Roads Project.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/b94b8e39c9d805aa/Documents/GitHub/Diverging-Roads/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="268" documentId="11_F25DC773A252ABDACC10484719DA7CD85BDE58F3" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{32023ABA-61CD-4CE5-90AA-A550A20869B3}"/>
+  <xr:revisionPtr revIDLastSave="270" documentId="11_F25DC773A252ABDACC10484719DA7CD85BDE58F3" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{EB729858-2D86-413F-9B47-7DCA0599EBBA}"/>
   <bookViews>
     <workbookView xWindow="825" yWindow="0" windowWidth="18540" windowHeight="14505" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="133" uniqueCount="55">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="132" uniqueCount="54">
   <si>
     <t>Title</t>
   </si>
@@ -199,9 +199,6 @@
   </si>
   <si>
     <t>Average</t>
-  </si>
-  <si>
-    <t>Fig 27b Angel mosaic not working in "Github" version</t>
   </si>
 </sst>
 </file>
@@ -943,7 +940,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="12" spans="1:14" ht="45" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A12" s="3">
         <v>11</v>
       </c>
@@ -964,9 +961,6 @@
       </c>
       <c r="G12" s="3" t="s">
         <v>33</v>
-      </c>
-      <c r="H12" s="1" t="s">
-        <v>54</v>
       </c>
       <c r="J12" s="3" t="s">
         <v>33</v>
@@ -1040,6 +1034,9 @@
       <c r="B15" s="2" t="s">
         <v>17</v>
       </c>
+      <c r="C15" s="2">
+        <v>1365</v>
+      </c>
       <c r="D15" s="2">
         <v>2024</v>
       </c>
@@ -1259,7 +1256,7 @@
       </c>
       <c r="C32" s="2">
         <f>SUM(C2:C31)</f>
-        <v>41084</v>
+        <v>42449</v>
       </c>
     </row>
     <row r="33" spans="1:3" x14ac:dyDescent="0.25">
@@ -1268,7 +1265,7 @@
       </c>
       <c r="C33" s="10">
         <f>AVERAGE(C2:C31)</f>
-        <v>3160.3076923076924</v>
+        <v>3032.0714285714284</v>
       </c>
     </row>
     <row r="35" spans="1:3" x14ac:dyDescent="0.25">

--- a/Div_Roads Project.xlsx
+++ b/Div_Roads Project.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/b94b8e39c9d805aa/Documents/GitHub/Diverging-Roads/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="270" documentId="11_F25DC773A252ABDACC10484719DA7CD85BDE58F3" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{EB729858-2D86-413F-9B47-7DCA0599EBBA}"/>
+  <xr:revisionPtr revIDLastSave="274" documentId="11_F25DC773A252ABDACC10484719DA7CD85BDE58F3" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{4BCB3A28-D88B-4537-8C01-69E8FDF48F55}"/>
   <bookViews>
     <workbookView xWindow="825" yWindow="0" windowWidth="18540" windowHeight="14505" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="132" uniqueCount="54">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="136" uniqueCount="54">
   <si>
     <t>Title</t>
   </si>
@@ -1043,6 +1043,18 @@
       <c r="E15" s="4" t="s">
         <v>33</v>
       </c>
+      <c r="F15" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="G15" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="J15" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="L15" s="3" t="s">
+        <v>33</v>
+      </c>
     </row>
     <row r="16" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A16" s="3">

--- a/Div_Roads Project.xlsx
+++ b/Div_Roads Project.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/b94b8e39c9d805aa/Documents/GitHub/Diverging-Roads/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="274" documentId="11_F25DC773A252ABDACC10484719DA7CD85BDE58F3" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{4BCB3A28-D88B-4537-8C01-69E8FDF48F55}"/>
+  <xr:revisionPtr revIDLastSave="276" documentId="11_F25DC773A252ABDACC10484719DA7CD85BDE58F3" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{11289856-4BB9-4AB2-9692-B79CFB98AC38}"/>
   <bookViews>
     <workbookView xWindow="825" yWindow="0" windowWidth="18540" windowHeight="14505" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="136" uniqueCount="54">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="138" uniqueCount="54">
   <si>
     <t>Title</t>
   </si>
@@ -1069,6 +1069,12 @@
       <c r="E16" s="4" t="s">
         <v>33</v>
       </c>
+      <c r="F16" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="G16" s="3" t="s">
+        <v>33</v>
+      </c>
     </row>
     <row r="17" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A17" s="3">

--- a/Div_Roads Project.xlsx
+++ b/Div_Roads Project.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/b94b8e39c9d805aa/Documents/GitHub/Diverging-Roads/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="276" documentId="11_F25DC773A252ABDACC10484719DA7CD85BDE58F3" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{11289856-4BB9-4AB2-9692-B79CFB98AC38}"/>
+  <xr:revisionPtr revIDLastSave="284" documentId="11_F25DC773A252ABDACC10484719DA7CD85BDE58F3" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{A920C018-72E9-4AEA-99D9-6CF603F8ED25}"/>
   <bookViews>
     <workbookView xWindow="825" yWindow="0" windowWidth="18540" windowHeight="14505" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="138" uniqueCount="54">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="141" uniqueCount="55">
   <si>
     <t>Title</t>
   </si>
@@ -199,6 +199,9 @@
   </si>
   <si>
     <t>Average</t>
+  </si>
+  <si>
+    <t>Wilhelm</t>
   </si>
 </sst>
 </file>
@@ -573,7 +576,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:N49"/>
+  <dimension ref="A1:N50"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="6.140625" style="3" customWidth="1"/>
@@ -1063,6 +1066,9 @@
       <c r="B16" s="2" t="s">
         <v>18</v>
       </c>
+      <c r="C16" s="2">
+        <v>1670</v>
+      </c>
       <c r="D16" s="2">
         <v>2024</v>
       </c>
@@ -1073,6 +1079,12 @@
         <v>33</v>
       </c>
       <c r="G16" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="J16" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="L16" s="3" t="s">
         <v>33</v>
       </c>
     </row>
@@ -1081,13 +1093,13 @@
         <v>16</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>19</v>
+        <v>54</v>
+      </c>
+      <c r="C17" s="2">
+        <v>2482</v>
       </c>
       <c r="D17" s="2">
         <v>2024</v>
-      </c>
-      <c r="E17" s="4" t="s">
-        <v>33</v>
       </c>
     </row>
     <row r="18" spans="1:10" x14ac:dyDescent="0.25">
@@ -1095,10 +1107,10 @@
         <v>17</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="D18" s="2">
-        <v>2025</v>
+        <v>2024</v>
       </c>
       <c r="E18" s="4" t="s">
         <v>33</v>
@@ -1109,7 +1121,7 @@
         <v>18</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="D19" s="2">
         <v>2025</v>
@@ -1123,7 +1135,7 @@
         <v>19</v>
       </c>
       <c r="B20" s="2" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="D20" s="2">
         <v>2025</v>
@@ -1137,7 +1149,7 @@
         <v>20</v>
       </c>
       <c r="B21" s="2" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="D21" s="2">
         <v>2025</v>
@@ -1146,12 +1158,12 @@
         <v>33</v>
       </c>
     </row>
-    <row r="22" spans="1:10" ht="30" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A22" s="3">
         <v>21</v>
       </c>
       <c r="B22" s="2" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="D22" s="2">
         <v>2025</v>
@@ -1159,16 +1171,13 @@
       <c r="E22" s="4" t="s">
         <v>33</v>
       </c>
-      <c r="H22" s="1" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="23" spans="1:10" x14ac:dyDescent="0.25">
+    </row>
+    <row r="23" spans="1:10" ht="30" x14ac:dyDescent="0.25">
       <c r="A23" s="3">
         <v>22</v>
       </c>
       <c r="B23" s="2" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="D23" s="2">
         <v>2025</v>
@@ -1176,8 +1185,8 @@
       <c r="E23" s="4" t="s">
         <v>33</v>
       </c>
-      <c r="J23" s="3" t="s">
-        <v>33</v>
+      <c r="H23" s="1" t="s">
+        <v>42</v>
       </c>
     </row>
     <row r="24" spans="1:10" x14ac:dyDescent="0.25">
@@ -1185,12 +1194,15 @@
         <v>23</v>
       </c>
       <c r="B24" s="2" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="D24" s="2">
-        <v>2026</v>
+        <v>2025</v>
       </c>
       <c r="E24" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="J24" s="3" t="s">
         <v>33</v>
       </c>
     </row>
@@ -1199,7 +1211,7 @@
         <v>24</v>
       </c>
       <c r="B25" s="2" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="D25" s="2">
         <v>2026</v>
@@ -1213,7 +1225,7 @@
         <v>25</v>
       </c>
       <c r="B26" s="2" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="D26" s="2">
         <v>2026</v>
@@ -1227,7 +1239,7 @@
         <v>26</v>
       </c>
       <c r="B27" s="2" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="D27" s="2">
         <v>2026</v>
@@ -1241,10 +1253,13 @@
         <v>27</v>
       </c>
       <c r="B28" s="2" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="D28" s="2">
         <v>2026</v>
+      </c>
+      <c r="E28" s="4" t="s">
+        <v>33</v>
       </c>
     </row>
     <row r="29" spans="1:10" x14ac:dyDescent="0.25">
@@ -1252,7 +1267,7 @@
         <v>28</v>
       </c>
       <c r="B29" s="2" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="D29" s="2">
         <v>2026</v>
@@ -1262,6 +1277,12 @@
       <c r="A30" s="3">
         <v>29</v>
       </c>
+      <c r="B30" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="D30" s="2">
+        <v>2026</v>
+      </c>
     </row>
     <row r="31" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A31" s="3">
@@ -1269,40 +1290,42 @@
       </c>
     </row>
     <row r="32" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="B32" s="2" t="s">
-        <v>52</v>
-      </c>
-      <c r="C32" s="2">
-        <f>SUM(C2:C31)</f>
-        <v>42449</v>
+      <c r="A32" s="3">
+        <v>31</v>
       </c>
     </row>
     <row r="33" spans="1:3" x14ac:dyDescent="0.25">
       <c r="B33" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="C33" s="2">
+        <f>SUM(C2:C32)</f>
+        <v>46601</v>
+      </c>
+    </row>
+    <row r="34" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="B34" s="2" t="s">
         <v>53</v>
       </c>
-      <c r="C33" s="10">
-        <f>AVERAGE(C2:C31)</f>
-        <v>3032.0714285714284</v>
-      </c>
-    </row>
-    <row r="35" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A35" s="8" t="s">
+      <c r="C34" s="10">
+        <f>AVERAGE(C2:C32)</f>
+        <v>2912.5625</v>
+      </c>
+    </row>
+    <row r="36" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A36" s="8" t="s">
         <v>48</v>
-      </c>
-    </row>
-    <row r="36" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A36" s="9" t="s">
-        <v>49</v>
       </c>
     </row>
     <row r="37" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A37" s="9" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="38" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A38" s="9" t="s">
         <v>50</v>
       </c>
-    </row>
-    <row r="38" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A38" s="9"/>
     </row>
     <row r="39" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A39" s="9"/>
@@ -1336,6 +1359,9 @@
     </row>
     <row r="49" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A49" s="9"/>
+    </row>
+    <row r="50" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A50" s="9"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/Div_Roads Project.xlsx
+++ b/Div_Roads Project.xlsx
@@ -8,15 +8,14 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/b94b8e39c9d805aa/Documents/GitHub/Diverging-Roads/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="284" documentId="11_F25DC773A252ABDACC10484719DA7CD85BDE58F3" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{A920C018-72E9-4AEA-99D9-6CF603F8ED25}"/>
+  <xr:revisionPtr revIDLastSave="289" documentId="11_F25DC773A252ABDACC10484719DA7CD85BDE58F3" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{C3EEFDC6-BC7D-4C9D-9363-F0997CB9942B}"/>
   <bookViews>
-    <workbookView xWindow="825" yWindow="0" windowWidth="18540" windowHeight="14505" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="2445" yWindow="0" windowWidth="15525" windowHeight="14505" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
   <calcPr calcId="191029"/>
-  <fileRecoveryPr repairLoad="1"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -37,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="141" uniqueCount="55">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="146" uniqueCount="55">
   <si>
     <t>Title</t>
   </si>
@@ -1088,7 +1087,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="17" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A17" s="3">
         <v>16</v>
       </c>
@@ -1101,8 +1100,23 @@
       <c r="D17" s="2">
         <v>2024</v>
       </c>
-    </row>
-    <row r="18" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="E17" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="F17" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="G17" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="J17" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="L17" s="3" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="18" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A18" s="3">
         <v>17</v>
       </c>
@@ -1116,7 +1130,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="19" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A19" s="3">
         <v>18</v>
       </c>
@@ -1130,7 +1144,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="20" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A20" s="3">
         <v>19</v>
       </c>
@@ -1144,7 +1158,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="21" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A21" s="3">
         <v>20</v>
       </c>
@@ -1158,7 +1172,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="22" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A22" s="3">
         <v>21</v>
       </c>
@@ -1172,7 +1186,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="23" spans="1:10" ht="30" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:12" ht="30" x14ac:dyDescent="0.25">
       <c r="A23" s="3">
         <v>22</v>
       </c>
@@ -1189,7 +1203,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="24" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A24" s="3">
         <v>23</v>
       </c>
@@ -1206,7 +1220,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="25" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A25" s="3">
         <v>24</v>
       </c>
@@ -1220,7 +1234,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="26" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A26" s="3">
         <v>25</v>
       </c>
@@ -1234,7 +1248,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="27" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A27" s="3">
         <v>26</v>
       </c>
@@ -1248,7 +1262,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="28" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A28" s="3">
         <v>27</v>
       </c>
@@ -1262,7 +1276,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="29" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A29" s="3">
         <v>28</v>
       </c>
@@ -1273,7 +1287,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="30" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A30" s="3">
         <v>29</v>
       </c>
@@ -1284,12 +1298,12 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="31" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A31" s="3">
         <v>30</v>
       </c>
     </row>
-    <row r="32" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A32" s="3">
         <v>31</v>
       </c>

--- a/Div_Roads Project.xlsx
+++ b/Div_Roads Project.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/b94b8e39c9d805aa/Documents/GitHub/Diverging-Roads/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="289" documentId="11_F25DC773A252ABDACC10484719DA7CD85BDE58F3" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{C3EEFDC6-BC7D-4C9D-9363-F0997CB9942B}"/>
+  <xr:revisionPtr revIDLastSave="294" documentId="11_F25DC773A252ABDACC10484719DA7CD85BDE58F3" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{DFC277BD-1704-4849-BE8D-808B20AD81BF}"/>
   <bookViews>
-    <workbookView xWindow="2445" yWindow="0" windowWidth="15525" windowHeight="14505" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="1170" yWindow="855" windowWidth="15525" windowHeight="14505" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="146" uniqueCount="55">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="150" uniqueCount="55">
   <si>
     <t>Title</t>
   </si>
@@ -1123,10 +1123,25 @@
       <c r="B18" s="2" t="s">
         <v>19</v>
       </c>
+      <c r="C18" s="2">
+        <v>8515</v>
+      </c>
       <c r="D18" s="2">
         <v>2024</v>
       </c>
       <c r="E18" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="F18" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="G18" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="J18" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="L18" s="3" t="s">
         <v>33</v>
       </c>
     </row>
@@ -1314,7 +1329,7 @@
       </c>
       <c r="C33" s="2">
         <f>SUM(C2:C32)</f>
-        <v>46601</v>
+        <v>55116</v>
       </c>
     </row>
     <row r="34" spans="1:3" x14ac:dyDescent="0.25">
@@ -1323,7 +1338,7 @@
       </c>
       <c r="C34" s="10">
         <f>AVERAGE(C2:C32)</f>
-        <v>2912.5625</v>
+        <v>3242.1176470588234</v>
       </c>
     </row>
     <row r="36" spans="1:3" x14ac:dyDescent="0.25">

--- a/Div_Roads Project.xlsx
+++ b/Div_Roads Project.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/b94b8e39c9d805aa/Documents/GitHub/Diverging-Roads/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="294" documentId="11_F25DC773A252ABDACC10484719DA7CD85BDE58F3" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{DFC277BD-1704-4849-BE8D-808B20AD81BF}"/>
+  <xr:revisionPtr revIDLastSave="316" documentId="11_F25DC773A252ABDACC10484719DA7CD85BDE58F3" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{0977BFEB-A452-4A47-B61D-EE2E52B588B1}"/>
   <bookViews>
-    <workbookView xWindow="1170" yWindow="855" windowWidth="15525" windowHeight="14505" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView minimized="1" xWindow="-45" yWindow="135" windowWidth="16740" windowHeight="14505" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="150" uniqueCount="55">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="164" uniqueCount="57">
   <si>
     <t>Title</t>
   </si>
@@ -201,6 +201,12 @@
   </si>
   <si>
     <t>Wilhelm</t>
+  </si>
+  <si>
+    <t>ECF Lebanon Man</t>
+  </si>
+  <si>
+    <t>6b</t>
   </si>
 </sst>
 </file>
@@ -827,8 +833,8 @@
       </c>
     </row>
     <row r="8" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A8" s="3">
-        <v>7</v>
+      <c r="A8" s="3" t="s">
+        <v>56</v>
       </c>
       <c r="B8" s="2" t="s">
         <v>13</v>
@@ -857,7 +863,7 @@
     </row>
     <row r="9" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A9" s="3">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B9" s="2" t="s">
         <v>10</v>
@@ -886,7 +892,7 @@
     </row>
     <row r="10" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A10" s="3">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B10" s="2" t="s">
         <v>11</v>
@@ -915,7 +921,7 @@
     </row>
     <row r="11" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A11" s="3">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B11" s="2" t="s">
         <v>12</v>
@@ -944,7 +950,7 @@
     </row>
     <row r="12" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A12" s="3">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B12" s="2" t="s">
         <v>14</v>
@@ -973,7 +979,7 @@
     </row>
     <row r="13" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A13" s="3">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B13" s="2" t="s">
         <v>15</v>
@@ -1002,7 +1008,7 @@
     </row>
     <row r="14" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A14" s="3">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B14" s="2" t="s">
         <v>16</v>
@@ -1031,7 +1037,7 @@
     </row>
     <row r="15" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A15" s="3">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B15" s="2" t="s">
         <v>17</v>
@@ -1060,7 +1066,7 @@
     </row>
     <row r="16" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A16" s="3">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B16" s="2" t="s">
         <v>18</v>
@@ -1089,7 +1095,7 @@
     </row>
     <row r="17" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A17" s="3">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B17" s="2" t="s">
         <v>54</v>
@@ -1118,7 +1124,7 @@
     </row>
     <row r="18" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A18" s="3">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B18" s="2" t="s">
         <v>19</v>
@@ -1147,49 +1153,94 @@
     </row>
     <row r="19" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A19" s="3">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B19" s="2" t="s">
         <v>20</v>
       </c>
+      <c r="C19" s="2">
+        <v>3598</v>
+      </c>
       <c r="D19" s="2">
         <v>2025</v>
       </c>
       <c r="E19" s="4" t="s">
         <v>33</v>
       </c>
+      <c r="F19" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="G19" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="J19" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="L19" s="3" t="s">
+        <v>33</v>
+      </c>
     </row>
     <row r="20" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A20" s="3">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="B20" s="2" t="s">
         <v>21</v>
       </c>
+      <c r="C20" s="2">
+        <v>3000</v>
+      </c>
       <c r="D20" s="2">
         <v>2025</v>
       </c>
       <c r="E20" s="4" t="s">
         <v>33</v>
       </c>
+      <c r="F20" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="G20" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="J20" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="L20" s="3" t="s">
+        <v>33</v>
+      </c>
     </row>
     <row r="21" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A21" s="3">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="B21" s="2" t="s">
         <v>22</v>
       </c>
+      <c r="C21" s="2">
+        <v>702</v>
+      </c>
       <c r="D21" s="2">
         <v>2025</v>
       </c>
       <c r="E21" s="4" t="s">
         <v>33</v>
       </c>
+      <c r="F21" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="G21" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="J21" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="L21" s="3" t="s">
+        <v>33</v>
+      </c>
     </row>
     <row r="22" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A22" s="3">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="B22" s="2" t="s">
         <v>23</v>
@@ -1203,7 +1254,7 @@
     </row>
     <row r="23" spans="1:12" ht="30" x14ac:dyDescent="0.25">
       <c r="A23" s="3">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="B23" s="2" t="s">
         <v>24</v>
@@ -1220,7 +1271,7 @@
     </row>
     <row r="24" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A24" s="3">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="B24" s="2" t="s">
         <v>25</v>
@@ -1237,7 +1288,7 @@
     </row>
     <row r="25" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A25" s="3">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="B25" s="2" t="s">
         <v>26</v>
@@ -1251,7 +1302,7 @@
     </row>
     <row r="26" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A26" s="3">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="B26" s="2" t="s">
         <v>27</v>
@@ -1265,7 +1316,7 @@
     </row>
     <row r="27" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A27" s="3">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="B27" s="2" t="s">
         <v>28</v>
@@ -1279,7 +1330,7 @@
     </row>
     <row r="28" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A28" s="3">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="B28" s="2" t="s">
         <v>29</v>
@@ -1293,7 +1344,7 @@
     </row>
     <row r="29" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A29" s="3">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="B29" s="2" t="s">
         <v>30</v>
@@ -1304,7 +1355,7 @@
     </row>
     <row r="30" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A30" s="3">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="B30" s="2" t="s">
         <v>31</v>
@@ -1315,12 +1366,13 @@
     </row>
     <row r="31" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A31" s="3">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="32" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A32" s="3">
-        <v>31</v>
+        <v>29</v>
+      </c>
+      <c r="B31" s="2" t="s">
+        <v>55</v>
+      </c>
+      <c r="D31" s="2">
+        <v>2026</v>
       </c>
     </row>
     <row r="33" spans="1:3" x14ac:dyDescent="0.25">
@@ -1329,7 +1381,7 @@
       </c>
       <c r="C33" s="2">
         <f>SUM(C2:C32)</f>
-        <v>55116</v>
+        <v>62416</v>
       </c>
     </row>
     <row r="34" spans="1:3" x14ac:dyDescent="0.25">
@@ -1338,7 +1390,7 @@
       </c>
       <c r="C34" s="10">
         <f>AVERAGE(C2:C32)</f>
-        <v>3242.1176470588234</v>
+        <v>3120.8</v>
       </c>
     </row>
     <row r="36" spans="1:3" x14ac:dyDescent="0.25">

--- a/Div_Roads Project.xlsx
+++ b/Div_Roads Project.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/b94b8e39c9d805aa/Documents/GitHub/Diverging-Roads/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="316" documentId="11_F25DC773A252ABDACC10484719DA7CD85BDE58F3" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{0977BFEB-A452-4A47-B61D-EE2E52B588B1}"/>
+  <xr:revisionPtr revIDLastSave="319" documentId="11_F25DC773A252ABDACC10484719DA7CD85BDE58F3" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{C75681D8-8E15-4FEE-9BC9-AD56FC7FF2E0}"/>
   <bookViews>
-    <workbookView minimized="1" xWindow="-45" yWindow="135" windowWidth="16740" windowHeight="14505" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="16740" windowHeight="14505" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="164" uniqueCount="57">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="165" uniqueCount="58">
   <si>
     <t>Title</t>
   </si>
@@ -207,6 +207,9 @@
   </si>
   <si>
     <t>6b</t>
+  </si>
+  <si>
+    <t>AI took over - I need to restore this to original</t>
   </si>
 </sst>
 </file>
@@ -1238,18 +1241,24 @@
         <v>33</v>
       </c>
     </row>
-    <row r="22" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:12" ht="30" x14ac:dyDescent="0.25">
       <c r="A22" s="3">
         <v>20</v>
       </c>
       <c r="B22" s="2" t="s">
         <v>23</v>
       </c>
+      <c r="C22" s="2">
+        <v>2786</v>
+      </c>
       <c r="D22" s="2">
         <v>2025</v>
       </c>
       <c r="E22" s="4" t="s">
         <v>33</v>
+      </c>
+      <c r="H22" s="7" t="s">
+        <v>57</v>
       </c>
     </row>
     <row r="23" spans="1:12" ht="30" x14ac:dyDescent="0.25">
@@ -1381,7 +1390,7 @@
       </c>
       <c r="C33" s="2">
         <f>SUM(C2:C32)</f>
-        <v>62416</v>
+        <v>65202</v>
       </c>
     </row>
     <row r="34" spans="1:3" x14ac:dyDescent="0.25">
@@ -1390,7 +1399,7 @@
       </c>
       <c r="C34" s="10">
         <f>AVERAGE(C2:C32)</f>
-        <v>3120.8</v>
+        <v>3104.8571428571427</v>
       </c>
     </row>
     <row r="36" spans="1:3" x14ac:dyDescent="0.25">

--- a/Div_Roads Project.xlsx
+++ b/Div_Roads Project.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/b94b8e39c9d805aa/Documents/GitHub/Diverging-Roads/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="319" documentId="11_F25DC773A252ABDACC10484719DA7CD85BDE58F3" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{C75681D8-8E15-4FEE-9BC9-AD56FC7FF2E0}"/>
+  <xr:revisionPtr revIDLastSave="324" documentId="11_F25DC773A252ABDACC10484719DA7CD85BDE58F3" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{6D144B11-9C3A-4CB9-A5F4-66A43FEF6F42}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="16740" windowHeight="14505" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="165" uniqueCount="58">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="168" uniqueCount="57">
   <si>
     <t>Title</t>
   </si>
@@ -207,9 +207,6 @@
   </si>
   <si>
     <t>6b</t>
-  </si>
-  <si>
-    <t>AI took over - I need to restore this to original</t>
   </si>
 </sst>
 </file>
@@ -1241,7 +1238,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="22" spans="1:12" ht="30" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A22" s="3">
         <v>20</v>
       </c>
@@ -1257,8 +1254,18 @@
       <c r="E22" s="4" t="s">
         <v>33</v>
       </c>
-      <c r="H22" s="7" t="s">
-        <v>57</v>
+      <c r="F22" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="G22" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="H22" s="7"/>
+      <c r="J22" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="L22" s="3" t="s">
+        <v>33</v>
       </c>
     </row>
     <row r="23" spans="1:12" ht="30" x14ac:dyDescent="0.25">

--- a/Div_Roads Project.xlsx
+++ b/Div_Roads Project.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/b94b8e39c9d805aa/Documents/GitHub/Diverging-Roads/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="324" documentId="11_F25DC773A252ABDACC10484719DA7CD85BDE58F3" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{6D144B11-9C3A-4CB9-A5F4-66A43FEF6F42}"/>
+  <xr:revisionPtr revIDLastSave="334" documentId="11_F25DC773A252ABDACC10484719DA7CD85BDE58F3" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{EA98F272-53E2-4C9E-A299-60A3A1DD0CF5}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="16740" windowHeight="14505" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="168" uniqueCount="57">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="173" uniqueCount="57">
   <si>
     <t>Title</t>
   </si>
@@ -164,9 +164,6 @@
     <t>Copyright added</t>
   </si>
   <si>
-    <t>Text in original and lebtown differ - reconcile</t>
-  </si>
-  <si>
     <t>Done, defined the small and medium plate sizes in readme file.</t>
   </si>
   <si>
@@ -207,6 +204,9 @@
   </si>
   <si>
     <t>6b</t>
+  </si>
+  <si>
+    <t>Redoing</t>
   </si>
 </sst>
 </file>
@@ -265,7 +265,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="11">
+  <cellXfs count="12">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
@@ -296,6 +296,9 @@
     </xf>
     <xf numFmtId="1" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -630,13 +633,13 @@
         <v>41</v>
       </c>
       <c r="K1" s="6" t="s">
+        <v>43</v>
+      </c>
+      <c r="L1" s="6" t="s">
         <v>44</v>
       </c>
-      <c r="L1" s="6" t="s">
+      <c r="M1" s="6" t="s">
         <v>45</v>
-      </c>
-      <c r="M1" s="6" t="s">
-        <v>46</v>
       </c>
       <c r="N1" s="6"/>
     </row>
@@ -701,7 +704,7 @@
         <v>40</v>
       </c>
       <c r="I3" s="7" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="J3" s="3" t="s">
         <v>33</v>
@@ -733,10 +736,10 @@
         <v>33</v>
       </c>
       <c r="H4" s="1" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="I4" s="1" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="J4" s="3" t="s">
         <v>33</v>
@@ -834,7 +837,7 @@
     </row>
     <row r="8" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A8" s="3" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="B8" s="2" t="s">
         <v>13</v>
@@ -1098,7 +1101,7 @@
         <v>15</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="C17" s="2">
         <v>2482</v>
@@ -1260,7 +1263,7 @@
       <c r="G22" s="3" t="s">
         <v>33</v>
       </c>
-      <c r="H22" s="7"/>
+      <c r="H22" s="11"/>
       <c r="J22" s="3" t="s">
         <v>33</v>
       </c>
@@ -1268,21 +1271,33 @@
         <v>33</v>
       </c>
     </row>
-    <row r="23" spans="1:12" ht="30" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A23" s="3">
         <v>21</v>
       </c>
       <c r="B23" s="2" t="s">
         <v>24</v>
       </c>
+      <c r="C23" s="2">
+        <v>1468</v>
+      </c>
       <c r="D23" s="2">
         <v>2025</v>
       </c>
       <c r="E23" s="4" t="s">
         <v>33</v>
       </c>
-      <c r="H23" s="1" t="s">
-        <v>42</v>
+      <c r="F23" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="G23" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="J23" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="L23" s="3" t="s">
+        <v>33</v>
       </c>
     </row>
     <row r="24" spans="1:12" x14ac:dyDescent="0.25">
@@ -1292,13 +1307,22 @@
       <c r="B24" s="2" t="s">
         <v>25</v>
       </c>
+      <c r="C24" s="2">
+        <v>2039</v>
+      </c>
       <c r="D24" s="2">
         <v>2025</v>
       </c>
       <c r="E24" s="4" t="s">
         <v>33</v>
       </c>
+      <c r="H24" s="1" t="s">
+        <v>56</v>
+      </c>
       <c r="J24" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="L24" s="3" t="s">
         <v>33</v>
       </c>
     </row>
@@ -1385,7 +1409,7 @@
         <v>29</v>
       </c>
       <c r="B31" s="2" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="D31" s="2">
         <v>2026</v>
@@ -1393,35 +1417,35 @@
     </row>
     <row r="33" spans="1:3" x14ac:dyDescent="0.25">
       <c r="B33" s="2" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="C33" s="2">
         <f>SUM(C2:C32)</f>
-        <v>65202</v>
+        <v>68709</v>
       </c>
     </row>
     <row r="34" spans="1:3" x14ac:dyDescent="0.25">
       <c r="B34" s="2" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="C34" s="10">
         <f>AVERAGE(C2:C32)</f>
-        <v>3104.8571428571427</v>
+        <v>2987.3478260869565</v>
       </c>
     </row>
     <row r="36" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A36" s="8" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
     </row>
     <row r="37" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A37" s="9" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
     </row>
     <row r="38" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A38" s="9" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
     </row>
     <row r="39" spans="1:3" x14ac:dyDescent="0.25">

--- a/Div_Roads Project.xlsx
+++ b/Div_Roads Project.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/b94b8e39c9d805aa/Documents/GitHub/Diverging-Roads/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="334" documentId="11_F25DC773A252ABDACC10484719DA7CD85BDE58F3" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{EA98F272-53E2-4C9E-A299-60A3A1DD0CF5}"/>
+  <xr:revisionPtr revIDLastSave="342" documentId="11_F25DC773A252ABDACC10484719DA7CD85BDE58F3" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{051124CC-AF37-4F0E-A7A4-3D5FF166926F}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="16740" windowHeight="14505" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView minimized="1" xWindow="0" yWindow="0" windowWidth="16740" windowHeight="14505" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="173" uniqueCount="57">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="178" uniqueCount="56">
   <si>
     <t>Title</t>
   </si>
@@ -204,9 +204,6 @@
   </si>
   <si>
     <t>6b</t>
-  </si>
-  <si>
-    <t>Redoing</t>
   </si>
 </sst>
 </file>
@@ -1316,8 +1313,11 @@
       <c r="E24" s="4" t="s">
         <v>33</v>
       </c>
-      <c r="H24" s="1" t="s">
-        <v>56</v>
+      <c r="F24" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="G24" s="3" t="s">
+        <v>33</v>
       </c>
       <c r="J24" s="3" t="s">
         <v>33</v>
@@ -1333,10 +1333,25 @@
       <c r="B25" s="2" t="s">
         <v>26</v>
       </c>
+      <c r="C25" s="2">
+        <v>2157</v>
+      </c>
       <c r="D25" s="2">
         <v>2026</v>
       </c>
       <c r="E25" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="F25" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="G25" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="J25" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="L25" s="3" t="s">
         <v>33</v>
       </c>
     </row>
@@ -1421,7 +1436,7 @@
       </c>
       <c r="C33" s="2">
         <f>SUM(C2:C32)</f>
-        <v>68709</v>
+        <v>70866</v>
       </c>
     </row>
     <row r="34" spans="1:3" x14ac:dyDescent="0.25">
@@ -1430,7 +1445,7 @@
       </c>
       <c r="C34" s="10">
         <f>AVERAGE(C2:C32)</f>
-        <v>2987.3478260869565</v>
+        <v>2952.75</v>
       </c>
     </row>
     <row r="36" spans="1:3" x14ac:dyDescent="0.25">

--- a/Div_Roads Project.xlsx
+++ b/Div_Roads Project.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30326"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30430"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/b94b8e39c9d805aa/Documents/GitHub/Diverging-Roads/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="342" documentId="11_F25DC773A252ABDACC10484719DA7CD85BDE58F3" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{051124CC-AF37-4F0E-A7A4-3D5FF166926F}"/>
+  <xr:revisionPtr revIDLastSave="372" documentId="11_F25DC773A252ABDACC10484719DA7CD85BDE58F3" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{999234FD-9180-4FA8-873E-4B3670D82551}"/>
   <bookViews>
-    <workbookView minimized="1" xWindow="0" yWindow="0" windowWidth="16740" windowHeight="14505" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="675" yWindow="1965" windowWidth="17940" windowHeight="10890" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="178" uniqueCount="56">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="196" uniqueCount="58">
   <si>
     <t>Title</t>
   </si>
@@ -122,9 +122,6 @@
     <t>Garfield Connection</t>
   </si>
   <si>
-    <t>Jackson House</t>
-  </si>
-  <si>
     <t>Horseshoe Pike</t>
   </si>
   <si>
@@ -204,6 +201,15 @@
   </si>
   <si>
     <t>6b</t>
+  </si>
+  <si>
+    <t>Jackson House (w Children's Center)</t>
+  </si>
+  <si>
+    <t>Morris Millen</t>
+  </si>
+  <si>
+    <t>FIND OUT HOW DAVIS DOES THE TAG to EXPAND THE IMAGE - See TWO ROADS Diverging</t>
   </si>
 </sst>
 </file>
@@ -262,7 +268,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="12">
+  <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
@@ -294,9 +300,6 @@
     <xf numFmtId="1" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -312,10 +315,6 @@
     </ext>
   </extLst>
 </styleSheet>
-</file>
-
-<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
-<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -581,7 +580,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:N50"/>
+  <dimension ref="A1:N51"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="6.140625" style="3" customWidth="1"/>
@@ -600,16 +599,16 @@
   <sheetData>
     <row r="1" spans="1:14" s="5" customFormat="1" ht="47.25" x14ac:dyDescent="0.25">
       <c r="A1" s="5" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="B1" s="5" t="s">
         <v>0</v>
       </c>
       <c r="C1" s="5" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="D1" s="5" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="E1" s="6" t="s">
         <v>1</v>
@@ -621,22 +620,22 @@
         <v>3</v>
       </c>
       <c r="H1" s="6" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="I1" s="6" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="J1" s="6" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="K1" s="6" t="s">
+        <v>42</v>
+      </c>
+      <c r="L1" s="6" t="s">
         <v>43</v>
       </c>
-      <c r="L1" s="6" t="s">
+      <c r="M1" s="6" t="s">
         <v>44</v>
-      </c>
-      <c r="M1" s="6" t="s">
-        <v>45</v>
       </c>
       <c r="N1" s="6"/>
     </row>
@@ -654,25 +653,25 @@
         <v>2022</v>
       </c>
       <c r="E2" s="4" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="F2" s="3" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="G2" s="3" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="H2" s="1" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="I2" s="1" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="J2" s="3" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="L2" s="3" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
     </row>
     <row r="3" spans="1:14" ht="90" x14ac:dyDescent="0.25">
@@ -689,25 +688,25 @@
         <v>2022</v>
       </c>
       <c r="E3" s="4" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="F3" s="3" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="G3" s="3" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="H3" s="1" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="I3" s="7" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="J3" s="3" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="L3" s="3" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
     </row>
     <row r="4" spans="1:14" ht="45" x14ac:dyDescent="0.25">
@@ -724,25 +723,25 @@
         <v>2022</v>
       </c>
       <c r="E4" s="4" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="F4" s="3" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="G4" s="3" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="H4" s="1" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="I4" s="1" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="J4" s="3" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="L4" s="3" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
     </row>
     <row r="5" spans="1:14" x14ac:dyDescent="0.25">
@@ -759,19 +758,19 @@
         <v>2022</v>
       </c>
       <c r="E5" s="4" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="F5" s="3" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="G5" s="3" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="J5" s="3" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="L5" s="3" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
     </row>
     <row r="6" spans="1:14" x14ac:dyDescent="0.25">
@@ -788,19 +787,19 @@
         <v>2022</v>
       </c>
       <c r="E6" s="4" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="F6" s="3" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="G6" s="3" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="J6" s="3" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="L6" s="3" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
     </row>
     <row r="7" spans="1:14" x14ac:dyDescent="0.25">
@@ -817,24 +816,24 @@
         <v>2022</v>
       </c>
       <c r="E7" s="4" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="F7" s="3" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="G7" s="3" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="J7" s="3" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="L7" s="3" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
     </row>
     <row r="8" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A8" s="3" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="B8" s="2" t="s">
         <v>13</v>
@@ -846,19 +845,19 @@
         <v>2022</v>
       </c>
       <c r="E8" s="4" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="F8" s="3" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="G8" s="3" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="J8" s="3" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="L8" s="3" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
     </row>
     <row r="9" spans="1:14" x14ac:dyDescent="0.25">
@@ -875,19 +874,19 @@
         <v>2023</v>
       </c>
       <c r="E9" s="4" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="F9" s="3" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="G9" s="3" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="J9" s="3" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="L9" s="3" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
     </row>
     <row r="10" spans="1:14" x14ac:dyDescent="0.25">
@@ -904,19 +903,19 @@
         <v>2023</v>
       </c>
       <c r="E10" s="4" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="F10" s="3" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="G10" s="3" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="J10" s="3" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="L10" s="3" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
     </row>
     <row r="11" spans="1:14" x14ac:dyDescent="0.25">
@@ -933,19 +932,19 @@
         <v>2023</v>
       </c>
       <c r="E11" s="4" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="F11" s="3" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="G11" s="3" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="J11" s="3" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="L11" s="3" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
     </row>
     <row r="12" spans="1:14" x14ac:dyDescent="0.25">
@@ -962,19 +961,19 @@
         <v>2023</v>
       </c>
       <c r="E12" s="4" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="F12" s="3" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="G12" s="3" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="J12" s="3" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="L12" s="3" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
     </row>
     <row r="13" spans="1:14" x14ac:dyDescent="0.25">
@@ -991,19 +990,19 @@
         <v>2023</v>
       </c>
       <c r="E13" s="4" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="F13" s="3" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="G13" s="3" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="J13" s="3" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="L13" s="3" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
     </row>
     <row r="14" spans="1:14" x14ac:dyDescent="0.25">
@@ -1020,19 +1019,19 @@
         <v>2023</v>
       </c>
       <c r="E14" s="4" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="F14" s="3" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="G14" s="3" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="J14" s="3" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="L14" s="3" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
     </row>
     <row r="15" spans="1:14" x14ac:dyDescent="0.25">
@@ -1049,19 +1048,19 @@
         <v>2024</v>
       </c>
       <c r="E15" s="4" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="F15" s="3" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="G15" s="3" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="J15" s="3" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="L15" s="3" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
     </row>
     <row r="16" spans="1:14" x14ac:dyDescent="0.25">
@@ -1078,19 +1077,19 @@
         <v>2024</v>
       </c>
       <c r="E16" s="4" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="F16" s="3" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="G16" s="3" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="J16" s="3" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="L16" s="3" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
     </row>
     <row r="17" spans="1:12" x14ac:dyDescent="0.25">
@@ -1098,7 +1097,7 @@
         <v>15</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="C17" s="2">
         <v>2482</v>
@@ -1107,19 +1106,19 @@
         <v>2024</v>
       </c>
       <c r="E17" s="4" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="F17" s="3" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="G17" s="3" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="J17" s="3" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="L17" s="3" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
     </row>
     <row r="18" spans="1:12" x14ac:dyDescent="0.25">
@@ -1136,19 +1135,19 @@
         <v>2024</v>
       </c>
       <c r="E18" s="4" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="F18" s="3" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="G18" s="3" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="J18" s="3" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="L18" s="3" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
     </row>
     <row r="19" spans="1:12" x14ac:dyDescent="0.25">
@@ -1165,19 +1164,19 @@
         <v>2025</v>
       </c>
       <c r="E19" s="4" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="F19" s="3" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="G19" s="3" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="J19" s="3" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="L19" s="3" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
     </row>
     <row r="20" spans="1:12" x14ac:dyDescent="0.25">
@@ -1194,19 +1193,19 @@
         <v>2025</v>
       </c>
       <c r="E20" s="4" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="F20" s="3" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="G20" s="3" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="J20" s="3" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="L20" s="3" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
     </row>
     <row r="21" spans="1:12" x14ac:dyDescent="0.25">
@@ -1223,19 +1222,19 @@
         <v>2025</v>
       </c>
       <c r="E21" s="4" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="F21" s="3" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="G21" s="3" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="J21" s="3" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="L21" s="3" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
     </row>
     <row r="22" spans="1:12" x14ac:dyDescent="0.25">
@@ -1252,20 +1251,19 @@
         <v>2025</v>
       </c>
       <c r="E22" s="4" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="F22" s="3" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="G22" s="3" t="s">
-        <v>33</v>
-      </c>
-      <c r="H22" s="11"/>
+        <v>32</v>
+      </c>
       <c r="J22" s="3" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="L22" s="3" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
     </row>
     <row r="23" spans="1:12" x14ac:dyDescent="0.25">
@@ -1282,19 +1280,19 @@
         <v>2025</v>
       </c>
       <c r="E23" s="4" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="F23" s="3" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="G23" s="3" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="J23" s="3" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="L23" s="3" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
     </row>
     <row r="24" spans="1:12" x14ac:dyDescent="0.25">
@@ -1311,19 +1309,19 @@
         <v>2025</v>
       </c>
       <c r="E24" s="4" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="F24" s="3" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="G24" s="3" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="J24" s="3" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="L24" s="3" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
     </row>
     <row r="25" spans="1:12" x14ac:dyDescent="0.25">
@@ -1340,19 +1338,19 @@
         <v>2026</v>
       </c>
       <c r="E25" s="4" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="F25" s="3" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="G25" s="3" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="J25" s="3" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="L25" s="3" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
     </row>
     <row r="26" spans="1:12" x14ac:dyDescent="0.25">
@@ -1362,11 +1360,26 @@
       <c r="B26" s="2" t="s">
         <v>27</v>
       </c>
+      <c r="C26" s="2">
+        <v>1650</v>
+      </c>
       <c r="D26" s="2">
         <v>2026</v>
       </c>
       <c r="E26" s="4" t="s">
-        <v>33</v>
+        <v>32</v>
+      </c>
+      <c r="F26" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="G26" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="J26" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="L26" s="3" t="s">
+        <v>32</v>
       </c>
     </row>
     <row r="27" spans="1:12" x14ac:dyDescent="0.25">
@@ -1374,13 +1387,29 @@
         <v>25</v>
       </c>
       <c r="B27" s="2" t="s">
-        <v>28</v>
+        <v>55</v>
+      </c>
+      <c r="C27" s="2">
+        <f>1045+1066</f>
+        <v>2111</v>
       </c>
       <c r="D27" s="2">
         <v>2026</v>
       </c>
       <c r="E27" s="4" t="s">
-        <v>33</v>
+        <v>32</v>
+      </c>
+      <c r="F27" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="G27" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="J27" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="L27" s="3" t="s">
+        <v>32</v>
       </c>
     </row>
     <row r="28" spans="1:12" x14ac:dyDescent="0.25">
@@ -1388,13 +1417,28 @@
         <v>26</v>
       </c>
       <c r="B28" s="2" t="s">
-        <v>29</v>
+        <v>28</v>
+      </c>
+      <c r="C28" s="2">
+        <v>2410</v>
       </c>
       <c r="D28" s="2">
         <v>2026</v>
       </c>
       <c r="E28" s="4" t="s">
-        <v>33</v>
+        <v>32</v>
+      </c>
+      <c r="F28" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="G28" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="J28" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="L28" s="3" t="s">
+        <v>32</v>
       </c>
     </row>
     <row r="29" spans="1:12" x14ac:dyDescent="0.25">
@@ -1402,10 +1446,22 @@
         <v>27</v>
       </c>
       <c r="B29" s="2" t="s">
-        <v>30</v>
+        <v>29</v>
+      </c>
+      <c r="C29" s="2">
+        <v>4009</v>
       </c>
       <c r="D29" s="2">
         <v>2026</v>
+      </c>
+      <c r="E29" s="4" t="s">
+        <v>32</v>
+      </c>
+      <c r="F29" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="G29" s="3" t="s">
+        <v>32</v>
       </c>
     </row>
     <row r="30" spans="1:12" x14ac:dyDescent="0.25">
@@ -1413,58 +1469,72 @@
         <v>28</v>
       </c>
       <c r="B30" s="2" t="s">
-        <v>31</v>
+        <v>30</v>
+      </c>
+      <c r="C30" s="2">
+        <v>3505</v>
       </c>
       <c r="D30" s="2">
         <v>2026</v>
       </c>
-    </row>
-    <row r="31" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="E30" s="4" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="31" spans="1:12" ht="60" x14ac:dyDescent="0.25">
       <c r="A31" s="3">
         <v>29</v>
       </c>
       <c r="B31" s="2" t="s">
-        <v>54</v>
-      </c>
-      <c r="D31" s="2">
+        <v>56</v>
+      </c>
+      <c r="H31" s="7" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="32" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A32" s="3">
+        <v>30</v>
+      </c>
+      <c r="B32" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="D32" s="2">
         <v>2026</v>
-      </c>
-    </row>
-    <row r="33" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="B33" s="2" t="s">
-        <v>51</v>
-      </c>
-      <c r="C33" s="2">
-        <f>SUM(C2:C32)</f>
-        <v>70866</v>
       </c>
     </row>
     <row r="34" spans="1:3" x14ac:dyDescent="0.25">
       <c r="B34" s="2" t="s">
-        <v>52</v>
-      </c>
-      <c r="C34" s="10">
-        <f>AVERAGE(C2:C32)</f>
-        <v>2952.75</v>
-      </c>
-    </row>
-    <row r="36" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A36" s="8" t="s">
-        <v>47</v>
+        <v>50</v>
+      </c>
+      <c r="C34" s="2">
+        <f>SUM(C2:C33)</f>
+        <v>84551</v>
+      </c>
+    </row>
+    <row r="35" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="B35" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="C35" s="10">
+        <f>AVERAGE(C2:C33)</f>
+        <v>2915.5517241379312</v>
       </c>
     </row>
     <row r="37" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A37" s="9" t="s">
-        <v>48</v>
+      <c r="A37" s="8" t="s">
+        <v>46</v>
       </c>
     </row>
     <row r="38" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A38" s="9" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
     </row>
     <row r="39" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A39" s="9"/>
+      <c r="A39" s="9" t="s">
+        <v>48</v>
+      </c>
     </row>
     <row r="40" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A40" s="9"/>
@@ -1498,6 +1568,9 @@
     </row>
     <row r="50" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A50" s="9"/>
+    </row>
+    <row r="51" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A51" s="9"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/Div_Roads Project.xlsx
+++ b/Div_Roads Project.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/b94b8e39c9d805aa/Documents/GitHub/Diverging-Roads/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="372" documentId="11_F25DC773A252ABDACC10484719DA7CD85BDE58F3" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{999234FD-9180-4FA8-873E-4B3670D82551}"/>
+  <xr:revisionPtr revIDLastSave="380" documentId="11_F25DC773A252ABDACC10484719DA7CD85BDE58F3" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{895EEF7A-ABC4-4EBD-89D7-E569A5424ED3}"/>
   <bookViews>
-    <workbookView xWindow="675" yWindow="1965" windowWidth="17940" windowHeight="10890" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="675" yWindow="1965" windowWidth="17940" windowHeight="12540" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="196" uniqueCount="58">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="199" uniqueCount="59">
   <si>
     <t>Title</t>
   </si>
@@ -210,6 +210,9 @@
   </si>
   <si>
     <t>FIND OUT HOW DAVIS DOES THE TAG to EXPAND THE IMAGE - See TWO ROADS Diverging</t>
+  </si>
+  <si>
+    <t>Add stats tag</t>
   </si>
 </sst>
 </file>
@@ -268,7 +271,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="11">
+  <cellXfs count="12">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
@@ -299,6 +302,9 @@
     </xf>
     <xf numFmtId="1" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -580,7 +586,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:N51"/>
+  <dimension ref="A1:O51"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="6.140625" style="3" customWidth="1"/>
@@ -592,12 +598,13 @@
     <col min="7" max="7" width="10" style="3" customWidth="1"/>
     <col min="8" max="8" width="25.85546875" style="1" customWidth="1"/>
     <col min="9" max="9" width="19.42578125" style="1" customWidth="1"/>
-    <col min="10" max="10" width="9.140625" style="3"/>
-    <col min="12" max="12" width="9.140625" style="3"/>
-    <col min="13" max="13" width="15.28515625" customWidth="1"/>
+    <col min="10" max="10" width="7.42578125" style="4" customWidth="1"/>
+    <col min="11" max="11" width="9.140625" style="3"/>
+    <col min="13" max="13" width="9.140625" style="3"/>
+    <col min="14" max="14" width="15.28515625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:14" s="5" customFormat="1" ht="47.25" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:15" s="5" customFormat="1" ht="47.25" x14ac:dyDescent="0.25">
       <c r="A1" s="5" t="s">
         <v>34</v>
       </c>
@@ -626,20 +633,23 @@
         <v>36</v>
       </c>
       <c r="J1" s="6" t="s">
+        <v>58</v>
+      </c>
+      <c r="K1" s="6" t="s">
         <v>40</v>
       </c>
-      <c r="K1" s="6" t="s">
+      <c r="L1" s="6" t="s">
         <v>42</v>
       </c>
-      <c r="L1" s="6" t="s">
+      <c r="M1" s="6" t="s">
         <v>43</v>
       </c>
-      <c r="M1" s="6" t="s">
+      <c r="N1" s="6" t="s">
         <v>44</v>
       </c>
-      <c r="N1" s="6"/>
-    </row>
-    <row r="2" spans="1:14" ht="30" x14ac:dyDescent="0.25">
+      <c r="O1" s="6"/>
+    </row>
+    <row r="2" spans="1:15" ht="30" x14ac:dyDescent="0.25">
       <c r="A2" s="3">
         <v>1</v>
       </c>
@@ -667,14 +677,14 @@
       <c r="I2" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="J2" s="3" t="s">
-        <v>32</v>
-      </c>
-      <c r="L2" s="3" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="3" spans="1:14" ht="90" x14ac:dyDescent="0.25">
+      <c r="K2" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="M2" s="3" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="3" spans="1:15" ht="90" x14ac:dyDescent="0.25">
       <c r="A3" s="3">
         <v>2</v>
       </c>
@@ -702,14 +712,15 @@
       <c r="I3" s="7" t="s">
         <v>49</v>
       </c>
-      <c r="J3" s="3" t="s">
-        <v>32</v>
-      </c>
-      <c r="L3" s="3" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="4" spans="1:14" ht="45" x14ac:dyDescent="0.25">
+      <c r="J3" s="11"/>
+      <c r="K3" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="M3" s="3" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="4" spans="1:15" ht="45" x14ac:dyDescent="0.25">
       <c r="A4" s="3">
         <v>3</v>
       </c>
@@ -737,14 +748,14 @@
       <c r="I4" s="1" t="s">
         <v>45</v>
       </c>
-      <c r="J4" s="3" t="s">
-        <v>32</v>
-      </c>
-      <c r="L4" s="3" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="5" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="K4" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="M4" s="3" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="5" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A5" s="3">
         <v>4</v>
       </c>
@@ -766,14 +777,14 @@
       <c r="G5" s="3" t="s">
         <v>32</v>
       </c>
-      <c r="J5" s="3" t="s">
-        <v>32</v>
-      </c>
-      <c r="L5" s="3" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="6" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="K5" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="M5" s="3" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="6" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A6" s="3">
         <v>5</v>
       </c>
@@ -795,14 +806,14 @@
       <c r="G6" s="3" t="s">
         <v>32</v>
       </c>
-      <c r="J6" s="3" t="s">
-        <v>32</v>
-      </c>
-      <c r="L6" s="3" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="7" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="K6" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="M6" s="3" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="7" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A7" s="3">
         <v>6</v>
       </c>
@@ -824,14 +835,14 @@
       <c r="G7" s="3" t="s">
         <v>32</v>
       </c>
-      <c r="J7" s="3" t="s">
-        <v>32</v>
-      </c>
-      <c r="L7" s="3" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="8" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="K7" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="M7" s="3" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="8" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A8" s="3" t="s">
         <v>54</v>
       </c>
@@ -853,14 +864,14 @@
       <c r="G8" s="3" t="s">
         <v>32</v>
       </c>
-      <c r="J8" s="3" t="s">
-        <v>32</v>
-      </c>
-      <c r="L8" s="3" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="9" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="K8" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="M8" s="3" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="9" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A9" s="3">
         <v>7</v>
       </c>
@@ -882,14 +893,14 @@
       <c r="G9" s="3" t="s">
         <v>32</v>
       </c>
-      <c r="J9" s="3" t="s">
-        <v>32</v>
-      </c>
-      <c r="L9" s="3" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="10" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="K9" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="M9" s="3" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="10" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A10" s="3">
         <v>8</v>
       </c>
@@ -911,14 +922,14 @@
       <c r="G10" s="3" t="s">
         <v>32</v>
       </c>
-      <c r="J10" s="3" t="s">
-        <v>32</v>
-      </c>
-      <c r="L10" s="3" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="11" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="K10" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="M10" s="3" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="11" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A11" s="3">
         <v>9</v>
       </c>
@@ -940,14 +951,14 @@
       <c r="G11" s="3" t="s">
         <v>32</v>
       </c>
-      <c r="J11" s="3" t="s">
-        <v>32</v>
-      </c>
-      <c r="L11" s="3" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="12" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="K11" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="M11" s="3" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="12" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A12" s="3">
         <v>10</v>
       </c>
@@ -969,14 +980,17 @@
       <c r="G12" s="3" t="s">
         <v>32</v>
       </c>
-      <c r="J12" s="3" t="s">
-        <v>32</v>
-      </c>
-      <c r="L12" s="3" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="13" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="J12" s="4" t="s">
+        <v>32</v>
+      </c>
+      <c r="K12" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="M12" s="3" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="13" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A13" s="3">
         <v>11</v>
       </c>
@@ -998,14 +1012,14 @@
       <c r="G13" s="3" t="s">
         <v>32</v>
       </c>
-      <c r="J13" s="3" t="s">
-        <v>32</v>
-      </c>
-      <c r="L13" s="3" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="14" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="K13" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="M13" s="3" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="14" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A14" s="3">
         <v>12</v>
       </c>
@@ -1027,14 +1041,14 @@
       <c r="G14" s="3" t="s">
         <v>32</v>
       </c>
-      <c r="J14" s="3" t="s">
-        <v>32</v>
-      </c>
-      <c r="L14" s="3" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="15" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="K14" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="M14" s="3" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="15" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A15" s="3">
         <v>13</v>
       </c>
@@ -1056,14 +1070,14 @@
       <c r="G15" s="3" t="s">
         <v>32</v>
       </c>
-      <c r="J15" s="3" t="s">
-        <v>32</v>
-      </c>
-      <c r="L15" s="3" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="16" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="K15" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="M15" s="3" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="16" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A16" s="3">
         <v>14</v>
       </c>
@@ -1085,14 +1099,14 @@
       <c r="G16" s="3" t="s">
         <v>32</v>
       </c>
-      <c r="J16" s="3" t="s">
-        <v>32</v>
-      </c>
-      <c r="L16" s="3" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="17" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="K16" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="M16" s="3" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="17" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A17" s="3">
         <v>15</v>
       </c>
@@ -1114,14 +1128,17 @@
       <c r="G17" s="3" t="s">
         <v>32</v>
       </c>
-      <c r="J17" s="3" t="s">
-        <v>32</v>
-      </c>
-      <c r="L17" s="3" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="18" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="J17" s="4" t="s">
+        <v>32</v>
+      </c>
+      <c r="K17" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="M17" s="3" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="18" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A18" s="3">
         <v>16</v>
       </c>
@@ -1143,14 +1160,14 @@
       <c r="G18" s="3" t="s">
         <v>32</v>
       </c>
-      <c r="J18" s="3" t="s">
-        <v>32</v>
-      </c>
-      <c r="L18" s="3" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="19" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="K18" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="M18" s="3" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="19" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A19" s="3">
         <v>17</v>
       </c>
@@ -1172,14 +1189,14 @@
       <c r="G19" s="3" t="s">
         <v>32</v>
       </c>
-      <c r="J19" s="3" t="s">
-        <v>32</v>
-      </c>
-      <c r="L19" s="3" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="20" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="K19" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="M19" s="3" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="20" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A20" s="3">
         <v>18</v>
       </c>
@@ -1201,14 +1218,14 @@
       <c r="G20" s="3" t="s">
         <v>32</v>
       </c>
-      <c r="J20" s="3" t="s">
-        <v>32</v>
-      </c>
-      <c r="L20" s="3" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="21" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="K20" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="M20" s="3" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="21" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A21" s="3">
         <v>19</v>
       </c>
@@ -1230,14 +1247,14 @@
       <c r="G21" s="3" t="s">
         <v>32</v>
       </c>
-      <c r="J21" s="3" t="s">
-        <v>32</v>
-      </c>
-      <c r="L21" s="3" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="22" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="K21" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="M21" s="3" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="22" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A22" s="3">
         <v>20</v>
       </c>
@@ -1259,14 +1276,14 @@
       <c r="G22" s="3" t="s">
         <v>32</v>
       </c>
-      <c r="J22" s="3" t="s">
-        <v>32</v>
-      </c>
-      <c r="L22" s="3" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="23" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="K22" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="M22" s="3" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="23" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A23" s="3">
         <v>21</v>
       </c>
@@ -1288,14 +1305,14 @@
       <c r="G23" s="3" t="s">
         <v>32</v>
       </c>
-      <c r="J23" s="3" t="s">
-        <v>32</v>
-      </c>
-      <c r="L23" s="3" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="24" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="K23" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="M23" s="3" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="24" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A24" s="3">
         <v>22</v>
       </c>
@@ -1317,14 +1334,14 @@
       <c r="G24" s="3" t="s">
         <v>32</v>
       </c>
-      <c r="J24" s="3" t="s">
-        <v>32</v>
-      </c>
-      <c r="L24" s="3" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="25" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="K24" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="M24" s="3" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="25" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A25" s="3">
         <v>23</v>
       </c>
@@ -1346,14 +1363,14 @@
       <c r="G25" s="3" t="s">
         <v>32</v>
       </c>
-      <c r="J25" s="3" t="s">
-        <v>32</v>
-      </c>
-      <c r="L25" s="3" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="26" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="K25" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="M25" s="3" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="26" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A26" s="3">
         <v>24</v>
       </c>
@@ -1375,14 +1392,14 @@
       <c r="G26" s="3" t="s">
         <v>32</v>
       </c>
-      <c r="J26" s="3" t="s">
-        <v>32</v>
-      </c>
-      <c r="L26" s="3" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="27" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="K26" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="M26" s="3" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="27" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A27" s="3">
         <v>25</v>
       </c>
@@ -1405,14 +1422,14 @@
       <c r="G27" s="3" t="s">
         <v>32</v>
       </c>
-      <c r="J27" s="3" t="s">
-        <v>32</v>
-      </c>
-      <c r="L27" s="3" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="28" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="K27" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="M27" s="3" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="28" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A28" s="3">
         <v>26</v>
       </c>
@@ -1434,14 +1451,14 @@
       <c r="G28" s="3" t="s">
         <v>32</v>
       </c>
-      <c r="J28" s="3" t="s">
-        <v>32</v>
-      </c>
-      <c r="L28" s="3" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="29" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="K28" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="M28" s="3" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="29" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A29" s="3">
         <v>27</v>
       </c>
@@ -1464,7 +1481,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="30" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A30" s="3">
         <v>28</v>
       </c>
@@ -1481,7 +1498,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="31" spans="1:12" ht="60" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:13" ht="60" x14ac:dyDescent="0.25">
       <c r="A31" s="3">
         <v>29</v>
       </c>
@@ -1492,7 +1509,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="32" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A32" s="3">
         <v>30</v>
       </c>

--- a/Div_Roads Project.xlsx
+++ b/Div_Roads Project.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/b94b8e39c9d805aa/Documents/GitHub/Diverging-Roads/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="380" documentId="11_F25DC773A252ABDACC10484719DA7CD85BDE58F3" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{895EEF7A-ABC4-4EBD-89D7-E569A5424ED3}"/>
+  <xr:revisionPtr revIDLastSave="383" documentId="11_F25DC773A252ABDACC10484719DA7CD85BDE58F3" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{D43E28ED-AC7A-44FB-A489-6004320E8605}"/>
   <bookViews>
     <workbookView xWindow="675" yWindow="1965" windowWidth="17940" windowHeight="12540" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="199" uniqueCount="59">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="198" uniqueCount="59">
   <si>
     <t>Title</t>
   </si>
@@ -980,9 +980,6 @@
       <c r="G12" s="3" t="s">
         <v>32</v>
       </c>
-      <c r="J12" s="4" t="s">
-        <v>32</v>
-      </c>
       <c r="K12" s="3" t="s">
         <v>32</v>
       </c>
@@ -1128,9 +1125,6 @@
       <c r="G17" s="3" t="s">
         <v>32</v>
       </c>
-      <c r="J17" s="4" t="s">
-        <v>32</v>
-      </c>
       <c r="K17" s="3" t="s">
         <v>32</v>
       </c>
@@ -1274,6 +1268,9 @@
         <v>32</v>
       </c>
       <c r="G22" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="J22" s="4" t="s">
         <v>32</v>
       </c>
       <c r="K22" s="3" t="s">

--- a/Div_Roads Project.xlsx
+++ b/Div_Roads Project.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/b94b8e39c9d805aa/Documents/GitHub/Diverging-Roads/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="383" documentId="11_F25DC773A252ABDACC10484719DA7CD85BDE58F3" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{D43E28ED-AC7A-44FB-A489-6004320E8605}"/>
+  <xr:revisionPtr revIDLastSave="387" documentId="11_F25DC773A252ABDACC10484719DA7CD85BDE58F3" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{EE454D2D-81A3-4695-94F1-3203B84EEB0B}"/>
   <bookViews>
-    <workbookView xWindow="675" yWindow="1965" windowWidth="17940" windowHeight="12540" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="2715" yWindow="540" windowWidth="17940" windowHeight="12540" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="198" uniqueCount="59">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="198" uniqueCount="58">
   <si>
     <t>Title</t>
   </si>
@@ -183,9 +183,6 @@
   </si>
   <si>
     <t>Add SHADOW attribute to all pictures</t>
-  </si>
-  <si>
-    <t>Forced to fit, but need a generic external stylesheet solution.  ADD CAPTIONS TO WORD DOC IMAGES</t>
   </si>
   <si>
     <t>Total:</t>
@@ -271,7 +268,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="12">
+  <cellXfs count="13">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
@@ -303,8 +300,11 @@
     <xf numFmtId="1" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -633,7 +633,7 @@
         <v>36</v>
       </c>
       <c r="J1" s="6" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="K1" s="6" t="s">
         <v>40</v>
@@ -677,6 +677,9 @@
       <c r="I2" s="1" t="s">
         <v>37</v>
       </c>
+      <c r="J2" s="4" t="s">
+        <v>32</v>
+      </c>
       <c r="K2" s="3" t="s">
         <v>32</v>
       </c>
@@ -684,7 +687,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="3" spans="1:15" ht="90" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:15" ht="30" x14ac:dyDescent="0.25">
       <c r="A3" s="3">
         <v>2</v>
       </c>
@@ -709,9 +712,7 @@
       <c r="H3" s="1" t="s">
         <v>39</v>
       </c>
-      <c r="I3" s="7" t="s">
-        <v>49</v>
-      </c>
+      <c r="I3" s="12"/>
       <c r="J3" s="11"/>
       <c r="K3" s="3" t="s">
         <v>32</v>
@@ -844,7 +845,7 @@
     </row>
     <row r="8" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A8" s="3" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="B8" s="2" t="s">
         <v>13</v>
@@ -1108,7 +1109,7 @@
         <v>15</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="C17" s="2">
         <v>2482</v>
@@ -1401,7 +1402,7 @@
         <v>25</v>
       </c>
       <c r="B27" s="2" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="C27" s="2">
         <f>1045+1066</f>
@@ -1500,10 +1501,10 @@
         <v>29</v>
       </c>
       <c r="B31" s="2" t="s">
+        <v>55</v>
+      </c>
+      <c r="H31" s="7" t="s">
         <v>56</v>
-      </c>
-      <c r="H31" s="7" t="s">
-        <v>57</v>
       </c>
     </row>
     <row r="32" spans="1:13" x14ac:dyDescent="0.25">
@@ -1511,7 +1512,7 @@
         <v>30</v>
       </c>
       <c r="B32" s="2" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="D32" s="2">
         <v>2026</v>
@@ -1519,7 +1520,7 @@
     </row>
     <row r="34" spans="1:3" x14ac:dyDescent="0.25">
       <c r="B34" s="2" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="C34" s="2">
         <f>SUM(C2:C33)</f>
@@ -1528,7 +1529,7 @@
     </row>
     <row r="35" spans="1:3" x14ac:dyDescent="0.25">
       <c r="B35" s="2" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="C35" s="10">
         <f>AVERAGE(C2:C33)</f>

--- a/Div_Roads Project.xlsx
+++ b/Div_Roads Project.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/b94b8e39c9d805aa/Documents/GitHub/Diverging-Roads/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="387" documentId="11_F25DC773A252ABDACC10484719DA7CD85BDE58F3" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{EE454D2D-81A3-4695-94F1-3203B84EEB0B}"/>
+  <xr:revisionPtr revIDLastSave="388" documentId="11_F25DC773A252ABDACC10484719DA7CD85BDE58F3" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{E7DE0332-5753-462C-8549-C66659C7F228}"/>
   <bookViews>
     <workbookView xWindow="2715" yWindow="540" windowWidth="17940" windowHeight="12540" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="198" uniqueCount="58">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="199" uniqueCount="58">
   <si>
     <t>Title</t>
   </si>
@@ -981,6 +981,9 @@
       <c r="G12" s="3" t="s">
         <v>32</v>
       </c>
+      <c r="J12" s="4" t="s">
+        <v>32</v>
+      </c>
       <c r="K12" s="3" t="s">
         <v>32</v>
       </c>

--- a/Div_Roads Project.xlsx
+++ b/Div_Roads Project.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/b94b8e39c9d805aa/Documents/GitHub/Diverging-Roads/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="388" documentId="11_F25DC773A252ABDACC10484719DA7CD85BDE58F3" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{E7DE0332-5753-462C-8549-C66659C7F228}"/>
+  <xr:revisionPtr revIDLastSave="392" documentId="11_F25DC773A252ABDACC10484719DA7CD85BDE58F3" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{E08E3ECE-4C43-4942-8AD8-4E8444B74EE1}"/>
   <bookViews>
-    <workbookView xWindow="2715" yWindow="540" windowWidth="17940" windowHeight="12540" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="3135" yWindow="2880" windowWidth="17940" windowHeight="12540" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="199" uniqueCount="58">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="199" uniqueCount="59">
   <si>
     <t>Title</t>
   </si>
@@ -210,6 +210,9 @@
   </si>
   <si>
     <t>Add stats tag</t>
+  </si>
+  <si>
+    <t>xx</t>
   </si>
 </sst>
 </file>
@@ -681,7 +684,7 @@
         <v>32</v>
       </c>
       <c r="K2" s="3" t="s">
-        <v>32</v>
+        <v>58</v>
       </c>
       <c r="M2" s="3" t="s">
         <v>32</v>
@@ -715,7 +718,7 @@
       <c r="I3" s="12"/>
       <c r="J3" s="11"/>
       <c r="K3" s="3" t="s">
-        <v>32</v>
+        <v>58</v>
       </c>
       <c r="M3" s="3" t="s">
         <v>32</v>
@@ -750,7 +753,7 @@
         <v>45</v>
       </c>
       <c r="K4" s="3" t="s">
-        <v>32</v>
+        <v>58</v>
       </c>
       <c r="M4" s="3" t="s">
         <v>32</v>
@@ -779,7 +782,7 @@
         <v>32</v>
       </c>
       <c r="K5" s="3" t="s">
-        <v>32</v>
+        <v>58</v>
       </c>
       <c r="M5" s="3" t="s">
         <v>32</v>

--- a/Div_Roads Project.xlsx
+++ b/Div_Roads Project.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/b94b8e39c9d805aa/Documents/GitHub/Diverging-Roads/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="392" documentId="11_F25DC773A252ABDACC10484719DA7CD85BDE58F3" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{E08E3ECE-4C43-4942-8AD8-4E8444B74EE1}"/>
+  <xr:revisionPtr revIDLastSave="396" documentId="11_F25DC773A252ABDACC10484719DA7CD85BDE58F3" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{5E6D03E2-2509-4033-970C-4FBFF281A42C}"/>
   <bookViews>
-    <workbookView xWindow="3135" yWindow="2880" windowWidth="17940" windowHeight="12540" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="19440" windowHeight="14880" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -271,7 +271,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="13">
+  <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
@@ -303,12 +303,6 @@
     <xf numFmtId="1" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -324,6 +318,10 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -715,8 +713,6 @@
       <c r="H3" s="1" t="s">
         <v>39</v>
       </c>
-      <c r="I3" s="12"/>
-      <c r="J3" s="11"/>
       <c r="K3" s="3" t="s">
         <v>58</v>
       </c>
